--- a/InputData/bldgs/CL/Component Lifetime.xlsx
+++ b/InputData/bldgs/CL/Component Lifetime.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\LA\bldgs\CL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\bldgs\CL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4529115-7E15-4208-A3C1-D479E9DA814A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455CF370-788E-4784-B578-F159A2380095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1800" yWindow="730" windowWidth="9800" windowHeight="10070" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="113">
   <si>
     <t>Lifetime (years)</t>
   </si>
@@ -376,9 +376,6 @@
   </si>
   <si>
     <t>Age at which reaches 95% retirement</t>
-  </si>
-  <si>
-    <t>Louisiana</t>
   </si>
 </sst>
 </file>
@@ -498,7 +495,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -546,7 +543,6 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -902,25 +898,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="2" max="2" width="61.54296875" customWidth="1"/>
     <col min="5" max="5" width="9.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C1" s="23">
-        <v>45467</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
         <v>57</v>
       </c>
@@ -928,60 +918,60 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B4" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B5" s="4">
         <v>2000</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B6" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B7" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B8" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B9" s="4"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B10" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B14" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B15" t="s">
         <v>25</v>
       </c>
